--- a/docs/data/gia_pha_ho_pham_van_lite.xlsx
+++ b/docs/data/gia_pha_ho_pham_van_lite.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="28065" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="GiaPhaHoPhamVan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -21,7 +22,7 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -49,9 +50,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -198,7 +199,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -268,16 +267,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -399,46 +402,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -449,28 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
-  <cols>
-    <col width="6.875" customWidth="1" min="1" max="1"/>
-    <col width="28.875" customWidth="1" min="2" max="2"/>
-    <col width="10.875" customWidth="1" min="3" max="3"/>
-    <col width="12.875" customWidth="1" min="4" max="4"/>
-    <col width="10.875" customWidth="1" min="5" max="6"/>
-    <col width="14.875" customWidth="1" min="7" max="7"/>
-    <col width="10.875" customWidth="1" min="8" max="8"/>
-    <col width="14.875" customWidth="1" min="9" max="9"/>
-    <col width="15.875" customWidth="1" min="10" max="10"/>
-    <col width="16.875" customWidth="1" min="11" max="11"/>
-    <col width="14.875" customWidth="1" min="12" max="12"/>
-    <col width="16.875" customWidth="1" min="13" max="13"/>
-    <col width="12.875" customWidth="1" min="14" max="14"/>
-    <col width="15.875" customWidth="1" min="15" max="15"/>
-    <col width="14.875" customWidth="1" min="16" max="16"/>
-    <col width="12.875" customWidth="1" min="17" max="17"/>
-    <col width="25.875" customWidth="1" min="18" max="18"/>
-    <col width="45.875" customWidth="1" min="19" max="19"/>
-  </cols>
+  <dimension ref="A1:S52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -588,12 +532,11 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2, 3</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>3</v>
       </c>
@@ -605,9 +548,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>S</t>
@@ -623,7 +563,6 @@
           <t>Đ</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>Đời thứ 1</t>
@@ -649,12 +588,9 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>11</v>
       </c>
@@ -666,9 +602,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>S</t>
@@ -684,7 +617,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>Quan hệ: Vợ cả</t>
@@ -710,12 +642,9 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>24</v>
       </c>
@@ -727,9 +656,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>S</t>
@@ -745,7 +671,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>Quan hệ: Vợ hai</t>
@@ -780,7 +705,6 @@
       <c r="G5" t="n">
         <v>5</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>19</v>
       </c>
@@ -792,9 +716,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>S</t>
@@ -810,7 +731,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>Đời thứ 2</t>
@@ -836,12 +756,9 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>8</v>
       </c>
@@ -853,9 +770,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>S</t>
@@ -871,7 +785,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>Quan hệ: Vợ</t>
@@ -906,7 +819,6 @@
       <c r="G7" t="n">
         <v>7</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>13</v>
       </c>
@@ -918,9 +830,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>S</t>
@@ -936,7 +845,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>Đời thứ 3</t>
@@ -962,12 +870,9 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>6</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>20</v>
       </c>
@@ -979,9 +884,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>S</t>
@@ -997,7 +899,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>Quan hệ: Vợ</t>
@@ -1032,7 +933,6 @@
       <c r="G9" t="n">
         <v>9</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>11</v>
       </c>
@@ -1044,9 +944,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>S</t>
@@ -1062,7 +959,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>Đời thứ 4</t>
@@ -1088,12 +984,9 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>8</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>19</v>
       </c>
@@ -1105,9 +998,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>S</t>
@@ -1123,7 +1013,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>Quan hệ: Vợ</t>
@@ -1155,8 +1044,6 @@
       <c r="F11" t="n">
         <v>9</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
         <v>23</v>
       </c>
@@ -1168,9 +1055,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>S</t>
@@ -1186,7 +1070,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>Đời thứ 5 | Thọ 19</t>
@@ -1221,7 +1104,6 @@
       <c r="G12" t="n">
         <v>12</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>12</v>
       </c>
@@ -1233,9 +1115,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>S</t>
@@ -1251,7 +1130,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>Đời thứ 5</t>
@@ -1277,12 +1155,9 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>11</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>20</v>
       </c>
@@ -1294,9 +1169,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>S</t>
@@ -1312,7 +1184,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>Quan hệ: Vợ</t>
@@ -1347,7 +1218,6 @@
       <c r="G14" t="n">
         <v>14</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>25</v>
       </c>
@@ -1359,9 +1229,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>S</t>
@@ -1377,7 +1244,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>Đời thứ 6</t>
@@ -1403,12 +1269,9 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>13</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>3</v>
       </c>
@@ -1420,9 +1283,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>S</t>
@@ -1438,7 +1298,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>Quan hệ: Vợ</t>
@@ -1473,7 +1332,6 @@
       <c r="G16" t="n">
         <v>16</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>20</v>
       </c>
@@ -1485,9 +1343,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>S</t>
@@ -1503,7 +1358,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>Đời thứ 6 | Thọ 70</t>
@@ -1529,12 +1383,9 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>15</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
         <v>2</v>
       </c>
@@ -1546,9 +1397,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>S</t>
@@ -1564,7 +1412,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>Quan hệ: Vợ cả | Thọ 69</t>
@@ -1590,11 +1437,9 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="G18" t="n">
         <v>15</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
         <v>9</v>
       </c>
@@ -1606,9 +1451,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>S</t>
@@ -1624,7 +1466,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>Quan hệ: Vợ hai | Thọ 65</t>
@@ -1656,8 +1497,6 @@
       <c r="F19" t="n">
         <v>12</v>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
         <v>25</v>
       </c>
@@ -1669,9 +1508,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>S</t>
@@ -1687,7 +1523,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>Đời thứ 6 | Quê quán/Ghi chú: Bà cô tổ họ Phạm</t>
@@ -1722,7 +1557,6 @@
       <c r="G20" t="n">
         <v>20</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>6</v>
       </c>
@@ -1734,9 +1568,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>S</t>
@@ -1752,7 +1583,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>Đời thứ 7</t>
@@ -1778,12 +1608,9 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>19</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>11</v>
       </c>
@@ -1795,9 +1622,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>S</t>
@@ -1813,7 +1637,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>Quan hệ: Vợ</t>
@@ -1845,20 +1668,11 @@
       <c r="F22" t="n">
         <v>16</v>
       </c>
-      <c r="G22" t="n">
-        <v>33</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>S</t>
@@ -1874,7 +1688,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>Đời thứ 7</t>
@@ -1883,16 +1696,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ông (Chồng Bà Phạm Thị Loan)</t>
+          <t>Phạm Thị Lan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1900,22 +1713,17 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="n">
-        <v>32</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" t="n">
+        <v>16</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>S</t>
@@ -1931,20 +1739,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Quan hệ: Chồng</t>
+          <t>Đời thứ 7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Phạm Thị Lan</t>
+          <t>Phạm Thị Phượng</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1963,20 +1770,11 @@
       <c r="F24" t="n">
         <v>16</v>
       </c>
-      <c r="G24" t="n">
-        <v>35</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>S</t>
@@ -1992,7 +1790,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>Đời thứ 7</t>
@@ -2001,11 +1798,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ông (Chồng Bà Phạm Thị Lan)</t>
+          <t>Phạm Kim Lim</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2018,22 +1815,26 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>19</v>
+      </c>
+      <c r="F25" t="n">
+        <v>20</v>
+      </c>
       <c r="G25" t="n">
-        <v>34</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>12</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>S</t>
@@ -2049,20 +1850,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Quan hệ: Chồng</t>
+          <t>Đời thứ 8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Phạm Thị Phượng</t>
+          <t>Phạm Thị Ngọ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2075,26 +1875,20 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>15</v>
-      </c>
-      <c r="F26" t="n">
-        <v>16</v>
-      </c>
       <c r="G26" t="n">
-        <v>37</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>8</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>S</t>
@@ -2110,20 +1904,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Đời thứ 7</t>
+          <t>Quan hệ: Vợ cả | Quê quán/Ghi chú: Cùng làng</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ông (Chồng Bà Phạm Thị Phượng)</t>
+          <t>Phạm Kim Xây</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2136,22 +1929,26 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>38</v>
+      </c>
+      <c r="F27" t="n">
+        <v>39</v>
+      </c>
       <c r="G27" t="n">
-        <v>36</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="I27" t="n">
+        <v>22</v>
+      </c>
+      <c r="J27" t="n">
+        <v>6</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>S</t>
@@ -2167,25 +1964,24 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Quan hệ: Chồng</t>
+          <t>Đời thứ 9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Phạm Kim Lim</t>
+          <t>Nguyễn Thị Vồi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2193,30 +1989,20 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>19</v>
-      </c>
-      <c r="F28" t="n">
-        <v>20</v>
-      </c>
       <c r="G28" t="n">
-        <v>39</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>69</v>
+      </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>S</t>
@@ -2232,25 +2018,24 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Đời thứ 8</t>
+          <t>Quan hệ: Vợ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Phạm Thị Ngọ</t>
+          <t>Phạm Văn Tiễu</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2258,26 +2043,32 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>69</v>
+      </c>
+      <c r="F29" t="n">
+        <v>70</v>
+      </c>
       <c r="G29" t="n">
-        <v>38</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1899</v>
+      </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>1953</v>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>S</t>
@@ -2293,25 +2084,24 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Quan hệ: Vợ cả | Quê quán/Ghi chú: Cùng làng</t>
+          <t>Đời thứ 10 | Thọ 55</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Phạm Kim Xây</t>
+          <t>Phạm Thị Chuyển</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2319,30 +2109,23 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>38</v>
-      </c>
-      <c r="F30" t="n">
-        <v>39</v>
-      </c>
       <c r="G30" t="n">
-        <v>70</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>122</v>
+      </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>1973</v>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>S</t>
@@ -2358,25 +2141,24 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Đời thứ 9</t>
+          <t>Quan hệ: Vợ | Quê quán/Ghi chú: Cùng làng</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>70</v>
+        <v>245</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Vồi</t>
+          <t>Phạm Văn Uyên (Nuôi)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2384,26 +2166,32 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>122</v>
+      </c>
+      <c r="F31" t="n">
+        <v>123</v>
+      </c>
       <c r="G31" t="n">
-        <v>69</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1940</v>
+      </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>1997</v>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>S</t>
@@ -2419,60 +2207,39 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Quan hệ: Vợ</t>
+          <t>Đời thứ 11 | Thọ 58</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122</v>
+        <v>246</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Phạm Văn Tiễu</t>
+          <t>Nguyễn Thị Chăm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Đã mất</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>69</v>
-      </c>
-      <c r="F32" t="n">
-        <v>70</v>
+          <t>Còn sống</t>
+        </is>
       </c>
       <c r="G32" t="n">
-        <v>123</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1899</v>
-      </c>
-      <c r="I32" t="n">
-        <v>5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>7</v>
+        <v>245</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
-        <v>1953</v>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>S</t>
@@ -2488,25 +2255,24 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Đời thứ 10 | Thọ 55</t>
+          <t>Quan hệ: Vợ | Quê quán/Ghi chú: Mụ – Thanh Tâm</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123</v>
+        <v>429</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Phạm Thị Chuyển</t>
+          <t>Phạm Văn Nấng</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2514,28 +2280,23 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="n">
-        <v>122</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>245</v>
+      </c>
+      <c r="F33" t="n">
+        <v>246</v>
+      </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="n">
-        <v>1973</v>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>S</t>
@@ -2551,60 +2312,54 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Quan hệ: Vợ | Quê quán/Ghi chú: Cùng làng</t>
+          <t>Đời thứ 12 | Quê quán/Ghi chú: Mất từ nhỏ</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>430</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Phạm Thị Chỉ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Đã mất</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
         <v>245</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Phạm Văn Uyên (Nuôi)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Đã mất</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>122</v>
-      </c>
       <c r="F34" t="n">
-        <v>123</v>
+        <v>246</v>
       </c>
       <c r="G34" t="n">
-        <v>246</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1940</v>
+        <v>431</v>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
-        <v>1997</v>
-      </c>
-      <c r="N34" t="inlineStr"/>
+        <v>1995</v>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>S</t>
@@ -2620,25 +2375,24 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Đời thứ 11 | Thọ 58</t>
+          <t>Đời thứ 12 | Quê quán/Ghi chú: Mất</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>246</v>
+        <v>431</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Chăm</t>
+          <t>Tạ Duy Hưng</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2646,22 +2400,14 @@
           <t>Còn sống</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>245</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+        <v>430</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>S</t>
@@ -2677,20 +2423,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Quan hệ: Vợ | Quê quán/Ghi chú: Mụ – Thanh Tâm</t>
+          <t>Quan hệ: Chồng | Quê quán/Ghi chú: Cùng làng | Lấy vợ</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Phạm Văn Nấng</t>
+          <t>Phạm Văn Khương</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2700,7 +2445,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Đã mất</t>
+          <t>Còn sống</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2709,22 +2454,17 @@
       <c r="F36" t="n">
         <v>246</v>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="n">
-        <v>17</v>
-      </c>
-      <c r="J36" t="n">
-        <v>3</v>
+      <c r="G36" t="n">
+        <v>433</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1964</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>S</t>
@@ -2740,20 +2480,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Đời thứ 12 | Quê quán/Ghi chú: Mất từ nhỏ</t>
+          <t>Đời thứ 12</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Phạm Thị Chỉ</t>
+          <t>Chu Thị Hà</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2763,35 +2502,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Đã mất</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>245</v>
-      </c>
-      <c r="F37" t="n">
-        <v>246</v>
+          <t>Còn sống</t>
+        </is>
       </c>
       <c r="G37" t="n">
-        <v>431</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="n">
-        <v>23</v>
-      </c>
-      <c r="J37" t="n">
-        <v>6</v>
+        <v>432</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1967</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="n">
-        <v>1995</v>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>S</t>
@@ -2807,20 +2531,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Đời thứ 12 | Quê quán/Ghi chú: Mất</t>
+          <t>Quan hệ: Vợ | Quê quán/Ghi chú: Duy Tiên – Hà Nam</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tạ Duy Hưng</t>
+          <t>Phạm Văn Cường</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2833,22 +2556,32 @@
           <t>Đã mất</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>245</v>
+      </c>
+      <c r="F38" t="n">
+        <v>246</v>
+      </c>
       <c r="G38" t="n">
-        <v>430</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+        <v>435</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1970</v>
+      </c>
+      <c r="I38" t="n">
+        <v>26</v>
+      </c>
+      <c r="J38" t="n">
+        <v>8</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>2016</v>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>S</t>
@@ -2864,25 +2597,24 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Quan hệ: Chồng | Quê quán/Ghi chú: Cùng làng | Lấy vợ</t>
+          <t>Đời thứ 12 | Quê quán/Ghi chú: Mất</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Phạm Văn Khương</t>
+          <t>Nguyễn Thị Kim</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2890,28 +2622,14 @@
           <t>Còn sống</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>245</v>
-      </c>
-      <c r="F39" t="n">
-        <v>246</v>
-      </c>
       <c r="G39" t="n">
-        <v>433</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1964</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+        <v>434</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>S</t>
@@ -2927,50 +2645,57 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Đời thứ 12</t>
+          <t>Quan hệ: Vợ | Quê quán/Ghi chú: Cùng làng | Tái giá năm 2024</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chu Thị Hà</t>
+          <t>Phạm Văn Tráng</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Còn sống</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Đã mất</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>245</v>
+      </c>
+      <c r="F40" t="n">
+        <v>246</v>
+      </c>
       <c r="G40" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="H40" t="n">
-        <v>1967</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+        <v>1975</v>
+      </c>
+      <c r="I40" t="n">
+        <v>21</v>
+      </c>
+      <c r="J40" t="n">
+        <v>12</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>2022</v>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>S</t>
@@ -2986,60 +2711,42 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Quan hệ: Vợ | Quê quán/Ghi chú: Duy Tiên – Hà Nam</t>
+          <t>Đời thứ 12 | Quê quán/Ghi chú: Đã chết</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Phạm Văn Cường</t>
+          <t>Phạm Thị Thuý</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nam</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Đã mất</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>245</v>
-      </c>
-      <c r="F41" t="n">
-        <v>246</v>
+          <t>Còn sống</t>
+        </is>
       </c>
       <c r="G41" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H41" t="n">
-        <v>1970</v>
-      </c>
-      <c r="I41" t="n">
-        <v>26</v>
-      </c>
-      <c r="J41" t="n">
-        <v>8</v>
+        <v>1979</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="n">
-        <v>2016</v>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>S</t>
@@ -3055,47 +2762,51 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Đời thứ 12 | Quê quán/Ghi chú: Mất</t>
+          <t>Quan hệ: Vợ | Quê quán/Ghi chú: Cổ Động – Thanh Hải</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Kim</t>
+          <t>Phạm Văn Sáng</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Còn sống</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="n">
-        <v>434</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>Đã mất</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>245</v>
+      </c>
+      <c r="F42" t="n">
+        <v>246</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1978</v>
+      </c>
+      <c r="I42" t="n">
+        <v>6</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>S</t>
@@ -3111,20 +2822,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Quan hệ: Vợ | Quê quán/Ghi chú: Cùng làng| Tái giá 2024</t>
+          <t>Đời thứ 12 | Quê quán/Ghi chú: Mất từ nhỏ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Phạm Văn Tráng</t>
+          <t>Phạm Văn Bẩy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3134,7 +2844,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Đã mất</t>
+          <t>Còn sống</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -3144,27 +2854,16 @@
         <v>246</v>
       </c>
       <c r="G43" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="H43" t="n">
-        <v>1975</v>
-      </c>
-      <c r="I43" t="n">
-        <v>21</v>
-      </c>
-      <c r="J43" t="n">
-        <v>12</v>
+        <v>1981</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="n">
-        <v>2022</v>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>S</t>
@@ -3180,20 +2879,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Đời thứ 12 | Quê quán/Ghi chú: Đã chết</t>
+          <t>Đời thứ 12</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Phạm Thị Thuý</t>
+          <t>Nguyễn Thị Thuý Hiền</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3206,24 +2904,17 @@
           <t>Còn sống</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="H44" t="n">
-        <v>1979</v>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+        <v>1983</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>S</t>
@@ -3239,20 +2930,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Quan hệ: Vợ | Quê quán/Ghi chú: Cổ Động – Thanh Hải</t>
+          <t>Quan hệ: Vợ | Quê quán/Ghi chú: Tỉnh Nghệ AN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>438</v>
+        <v>785</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Phạm Văn Sáng</t>
+          <t>Phạm Tiến Giáp</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3262,33 +2952,23 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Đã mất</t>
+          <t>Còn sống</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>245</v>
+        <v>432</v>
       </c>
       <c r="F45" t="n">
-        <v>246</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
+        <v>433</v>
+      </c>
       <c r="H45" t="n">
-        <v>1978</v>
-      </c>
-      <c r="I45" t="n">
-        <v>6</v>
-      </c>
-      <c r="J45" t="n">
-        <v>4</v>
+        <v>1990</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>S</t>
@@ -3304,20 +2984,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Đời thứ 12 | Quê quán/Ghi chú: Mất từ nhỏ</t>
+          <t>Đời thứ 13</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>439</v>
+        <v>787</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Phạm Văn Bẩy</t>
+          <t>Phạm Tiến Dũng</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3331,27 +3010,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>245</v>
+        <v>432</v>
       </c>
       <c r="F46" t="n">
-        <v>246</v>
-      </c>
-      <c r="G46" t="n">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="H46" t="n">
-        <v>1981</v>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+        <v>1994</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>S</t>
@@ -3367,20 +3038,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Đời thứ 12</t>
+          <t>Đời thứ 13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>440</v>
+        <v>789</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thuý Hiền</t>
+          <t>Phạm Thị Kim Dung</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3393,24 +3063,23 @@
           <t>Còn sống</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>434</v>
+      </c>
+      <c r="F47" t="n">
+        <v>435</v>
+      </c>
       <c r="G47" t="n">
-        <v>439</v>
+        <v>790</v>
       </c>
       <c r="H47" t="n">
-        <v>1983</v>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+        <v>1992</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>S</t>
@@ -3426,20 +3095,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Quan hệ: Vợ | Quê quán/Ghi chú: Tỉnh Nghệ AN</t>
+          <t>Đời thứ 13</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Phạm Tiến Giáp</t>
+          <t>Bùi Trường Minh</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3452,28 +3120,14 @@
           <t>Còn sống</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>432</v>
-      </c>
-      <c r="F48" t="n">
-        <v>433</v>
-      </c>
       <c r="G48" t="n">
-        <v>786</v>
-      </c>
-      <c r="H48" t="n">
-        <v>1990</v>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+        <v>789</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>S</t>
@@ -3489,25 +3143,24 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Đời thứ 13</t>
+          <t>Quan hệ: Chồng | Quê quán/Ghi chú: Thanh Hoá ( Hà Nội)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bà (Vợ Cụ Phạm Tiến Giáp)</t>
+          <t>Phạm Văn Đồng</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3515,22 +3168,20 @@
           <t>Còn sống</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="n">
-        <v>785</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>434</v>
+      </c>
+      <c r="F49" t="n">
+        <v>435</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1996</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>S</t>
@@ -3546,20 +3197,19 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Quan hệ: Vợ</t>
+          <t>Đời thứ 13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Phạm Tiến Dũng</t>
+          <t>Phạm Văn Phong</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3573,27 +3223,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F50" t="n">
-        <v>433</v>
-      </c>
-      <c r="G50" t="n">
-        <v>788</v>
+        <v>435</v>
       </c>
       <c r="H50" t="n">
-        <v>1994</v>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+        <v>2011</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>S</t>
@@ -3609,7 +3251,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>Đời thứ 13</t>
@@ -3618,16 +3259,16 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bà (Vợ Cụ Phạm Tiến Dũng)</t>
+          <t>Phạm Hải Nam</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3635,22 +3276,20 @@
           <t>Còn sống</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="n">
-        <v>787</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>436</v>
+      </c>
+      <c r="F51" t="n">
+        <v>437</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2009</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>S</t>
@@ -3666,25 +3305,24 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Quan hệ: Vợ</t>
+          <t>Đời thứ 13</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Phạm Thị Kim Dung</t>
+          <t>Phạm Hà Phương</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nữ</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3693,27 +3331,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F52" t="n">
-        <v>435</v>
-      </c>
-      <c r="G52" t="n">
-        <v>790</v>
+        <v>437</v>
       </c>
       <c r="H52" t="n">
-        <v>1992</v>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+        <v>2013</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>S</t>
@@ -3729,552 +3359,13 @@
           <t>S</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>Đời thứ 13</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>790</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Bùi Trường Minh</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Còn sống</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="n">
-        <v>789</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>Quan hệ: Chồng | Quê quán/Ghi chú: Thanh Hoá ( Hà Nội)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>791</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Phạm Văn Đồng</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Còn sống</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>434</v>
-      </c>
-      <c r="F54" t="n">
-        <v>435</v>
-      </c>
-      <c r="G54" t="n">
-        <v>792</v>
-      </c>
-      <c r="H54" t="n">
-        <v>1996</v>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>Đời thứ 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>792</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Bà (Vợ Cụ Phạm Văn Đồng)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Còn sống</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="n">
-        <v>791</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>Quan hệ: Vợ</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>793</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Phạm Văn Phong</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Còn sống</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>434</v>
-      </c>
-      <c r="F56" t="n">
-        <v>435</v>
-      </c>
-      <c r="G56" t="n">
-        <v>794</v>
-      </c>
-      <c r="H56" t="n">
-        <v>2011</v>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>Đời thứ 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>794</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Bà (Vợ Cụ Phạm Văn Phong)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Còn sống</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="n">
-        <v>793</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>Quan hệ: Vợ</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" t="n">
-        <v>795</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Phạm Hải Nam</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Còn sống</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>436</v>
-      </c>
-      <c r="F58" t="n">
-        <v>437</v>
-      </c>
-      <c r="G58" t="n">
-        <v>796</v>
-      </c>
-      <c r="H58" t="n">
-        <v>2009</v>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Đời thứ 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>796</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Bà (Vợ Cụ Phạm Hải Nam)</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Nữ</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Còn sống</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="n">
-        <v>795</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>Quan hệ: Vợ</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>797</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Phạm Hà Phương</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Còn sống</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>436</v>
-      </c>
-      <c r="F60" t="n">
-        <v>437</v>
-      </c>
-      <c r="G60" t="n">
-        <v>798</v>
-      </c>
-      <c r="H60" t="n">
-        <v>2013</v>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>Đời thứ 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>798</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Ông (Chồng Bà Phạm Hà Phương)</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Nam</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Còn sống</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="n">
-        <v>797</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>Quan hệ: Chồng</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>